--- a/public/sap-reporting/expansion-150-downloads/EXT-CO30-01.xlsx
+++ b/public/sap-reporting/expansion-150-downloads/EXT-CO30-01.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Layout" sheetId="1" r:id="R8522718ac14b44f5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flat input" sheetId="2" r:id="R4dc191802fff4950"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fields" sheetId="3" r:id="R38faed15808348f8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Layout" sheetId="1" r:id="Re32c46b16cb14527"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flat input" sheetId="2" r:id="R7bdda2ff0ecf484c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fields" sheetId="3" r:id="R092f697b1cfe4733"/>
   </x:sheets>
 </x:workbook>
 </file>
